--- a/assets/files/templates/SafePlum_patrol_checklist.xlsx
+++ b/assets/files/templates/SafePlum_patrol_checklist.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="83">
   <si>
     <r>
       <rPr>
@@ -2068,9 +2068,6 @@
     <t xml:space="preserve">경과일</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">가공동 통로</t>
   </si>
   <si>
@@ -2113,9 +2110,6 @@
     <t xml:space="preserve">물류팀 ○○○</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-30</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -2147,9 +2141,6 @@
       </rPr>
       <t xml:space="preserve">바닥 구획선 재도색</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-29</t>
   </si>
   <si>
     <r>
@@ -3681,32 +3672,32 @@
       <c r="A6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="25" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="D6" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="G6" s="25" t="n">
+        <v>46325</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="I6" s="25" t="n">
+        <v>46324</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>81</v>
       </c>
       <c r="K6" s="27" t="str">
         <f aca="true">IF(D6="","",IF(I6&lt;&gt;"","완료",IF(G6="","기한 미정",IF(G6&lt;TODAY(),"기한 경과",IF(G6-TODAY()&lt;=3,"임박","진행 중")))))</f>
@@ -4445,28 +4436,28 @@
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C41" s="30" t="n">
         <f aca="false">COUNTA(D6:D39)</f>
         <v>1</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E41" s="30" t="n">
         <f aca="false">COUNTIF(K6:K39,"완료")</f>
         <v>1</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G41" s="30" t="n">
         <f aca="false">COUNTIF(K6:K39,"진행 중")+COUNTIF(K6:K39,"임박")</f>
         <v>0</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I41" s="31" t="n">
         <f aca="false">COUNTIF(K6:K39,"기한 경과")</f>

--- a/assets/files/templates/SafePlum_patrol_checklist.xlsx
+++ b/assets/files/templates/SafePlum_patrol_checklist.xlsx
@@ -2973,12 +2973,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2991,12 +2991,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
